--- a/Spec/haystacked_AP0_field_spec_v0_10.xlsx
+++ b/Spec/haystacked_AP0_field_spec_v0_10.xlsx
@@ -6170,9 +6170,9 @@
   </sheetData>
   <mergeCells count="4">
     <mergeCell ref="B50:F50"/>
+    <mergeCell ref="B5:F5"/>
+    <mergeCell ref="B6:F6"/>
     <mergeCell ref="B3:F3"/>
-    <mergeCell ref="B6:F6"/>
-    <mergeCell ref="B5:F5"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup orientation="portrait" paperSize="9" horizontalDpi="300" verticalDpi="300"/>
@@ -8447,7 +8447,7 @@
         </is>
       </c>
       <c r="M4" t="n">
-        <v>500</v>
+        <v>40</v>
       </c>
       <c r="N4" t="n">
         <v>30000</v>
@@ -9137,7 +9137,7 @@
       </c>
       <c r="G21" s="68" t="inlineStr">
         <is>
-          <t>Single forks with NO support legs/structure under the load (true counterbalance free-lift). Source: drive_type=Counterbalanced + 'free lift'. Required to pick closed-bottom pallets on the floor and mate with closed conveyors — straddle/reach trucks fail here. Cond. K.O.: decisive only when the buyer has closed pallets/conveyors.</t>
+          <t>True when nothing sits under the load during transfer — free front face. Covers BOTH Counterbalanced trucks (rear counterweight, free front) AND Reach trucks (forks reach forward beyond the straddle legs, so the legs are never under the load). False only for straddle-under-load designs (support legs run under the pallet, e.g. straddle stacker / pallet mover) — those legs collide with closed-bottom pallets and closed conveyors. Source: drive_type=Counterbalanced or Reach + 'free lift'/'reach' description. Required to pick closed-bottom pallets on the floor and mate with closed conveyors — only straddle-under-load designs fail here, NOT reach trucks. Cond. K.O.: decisive only when the buyer has closed pallets/conveyors.</t>
         </is>
       </c>
       <c r="H21" s="52" t="inlineStr">
@@ -10328,7 +10328,7 @@
         </is>
       </c>
       <c r="M19" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
         <v>20000</v>
@@ -10671,7 +10671,7 @@
       </c>
       <c r="G6" s="68" t="inlineStr">
         <is>
-          <t>Can rotate the carried rack/pod in place to present a chosen face (hallmark of G2P). Source: 'shelf rotation / spin'. rotation_capable + grid_required ≈ goods-to-person; both false ≈ pure transport.</t>
+          <t>Can rotate the CARRIED rack/pod/shelf in place to present a chosen face to a picker (hallmark of G2P) — this is about the LOAD being rotated, not the vehicle. Do not set true merely because the vehicle chassis itself can pivot, spin in place, or has a small/zero turning radius — that is chassis mobility, a separate capability (see min_turning_radius); the vehicle must actually rotate the pod/rack it carries. Source: 'shelf rotation / pod rotation / rack spin'. rotation_capable + grid_required ≈ goods-to-person; both false ≈ pure transport.</t>
         </is>
       </c>
       <c r="I6" s="50" t="n">
@@ -10786,7 +10786,7 @@
         </is>
       </c>
       <c r="M9" t="n">
-        <v>100</v>
+        <v>60</v>
       </c>
       <c r="N9" t="n">
         <v>15000</v>
@@ -11073,7 +11073,7 @@
         </is>
       </c>
       <c r="M16" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
         <v>20000</v>
